--- a/modules/report/template-based-excel-generator/src/test/resources/templates/template.xlsx
+++ b/modules/report/template-based-excel-generator/src/test/resources/templates/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hyh/dev/mylib/kotlin/kotlin-common-library/modules/report/template-based-excel-generator/src/test/resources/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D174E537-DD9E-B649-A62E-DAB87BE3EC0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8D35DEB-F52C-684B-ADBA-CD9C1F80EA94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="70160" yWindow="3680" windowWidth="20980" windowHeight="17020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="275" r:id="rId8"/>
+    <pivotCache cacheId="19" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -528,16 +528,13 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -547,6 +544,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2308,7 +2308,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B913C3A8-83B3-D24B-8F4B-0985F48AA6EC}" name="피벗 테이블3" cacheId="275" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" grandTotalCaption="총" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="직급">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B913C3A8-83B3-D24B-8F4B-0985F48AA6EC}" name="피벗 테이블3" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" grandTotalCaption="총" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="직급">
   <location ref="I6:K8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField showAll="0"/>
@@ -2524,7 +2524,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E7D345E0-1F9E-3542-9E98-DBF333DED568}" name="피벗 테이블2" cacheId="275" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E7D345E0-1F9E-3542-9E98-DBF333DED568}" name="피벗 테이블2" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="값" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="M6:N8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" showAll="0"/>
@@ -2895,7 +2895,7 @@
     <we:reference id="WA200009404" version="1.0.0.5" store="" storeType="OMEX"/>
   </we:alternateReferences>
   <we:properties>
-    <we:property name="Office.AutoShowTaskpaneWithDocument" value="true"/>
+    <we:property name="claude.fileId" value="&quot;dfe74da6-0978-4135-92de-3fae4f02f194&quot;"/>
   </we:properties>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
@@ -2918,22 +2918,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="50" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="23" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="23"/>
+      <c r="D1" s="24"/>
       <c r="E1" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="26" t="str">
+      <c r="F1" s="29" t="str">
         <f>HYPERLINK("${url}", "${linkText}")</f>
         <v>${linkText}</v>
       </c>
-      <c r="G1" s="26"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:14" ht="32" customHeight="1">
       <c r="A2" s="25" t="s">
@@ -3085,15 +3085,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="23" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="23"/>
+      <c r="E1" s="24"/>
       <c r="F1" t="s">
         <v>42</v>
       </c>
@@ -3171,26 +3171,26 @@
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="23"/>
+      <c r="C23" s="24"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
     </row>
     <row r="30" spans="1:3">
       <c r="B30" t="s">
@@ -3226,14 +3226,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="50" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="23" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="23"/>
+      <c r="D1" s="24"/>
       <c r="E1" t="s">
         <v>42</v>
       </c>
@@ -3256,7 +3256,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="26" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -3265,14 +3265,14 @@
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="28"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="2"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="28" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -3281,7 +3281,7 @@
       <c r="C7" s="5"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="23"/>
+      <c r="A8" s="24"/>
       <c r="B8" s="12" t="s">
         <v>5</v>
       </c>
@@ -3342,22 +3342,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="50" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="23" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="23"/>
+      <c r="D1" s="24"/>
       <c r="E1" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="26" t="str">
+      <c r="F1" s="29" t="str">
         <f>HYPERLINK("${url}", "${linkText}")</f>
         <v>${linkText}</v>
       </c>
-      <c r="G1" s="26"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="32" customHeight="1">
       <c r="A2" s="25" t="s">
@@ -3463,24 +3463,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="50" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="23" t="e" cm="1">
+      <c r="B1" s="23"/>
+      <c r="C1" s="24" t="e" cm="1">
         <f t="array" aca="1" ref="C1" ca="1">TBEG_IMAGE(ci)</f>
         <v>#NAME?</v>
       </c>
-      <c r="D1" s="23"/>
+      <c r="D1" s="24"/>
       <c r="E1" t="e" cm="1">
         <f t="array" aca="1" ref="E1" ca="1">TBEG_IMAGE(logo)</f>
         <v>#NAME?</v>
       </c>
-      <c r="F1" s="26" t="str">
+      <c r="F1" s="29" t="str">
         <f>HYPERLINK("${url}", "${linkText}")</f>
         <v>${linkText}</v>
       </c>
-      <c r="G1" s="26"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:7" ht="32" customHeight="1">
       <c r="A2" s="25" t="s">
@@ -3588,24 +3588,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="50" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="23" t="e" cm="1">
+      <c r="B1" s="23"/>
+      <c r="C1" s="24" t="e" cm="1">
         <f t="array" aca="1" ref="C1" ca="1">TBEG_IMAGE(ci)</f>
         <v>#NAME?</v>
       </c>
-      <c r="D1" s="23"/>
+      <c r="D1" s="24"/>
       <c r="E1" t="e" cm="1">
         <f t="array" aca="1" ref="E1" ca="1">TBEG_IMAGE(logo)</f>
         <v>#NAME?</v>
       </c>
-      <c r="F1" s="26" t="str">
+      <c r="F1" s="29" t="str">
         <f>HYPERLINK("${url}", "${linkText}")</f>
         <v>${linkText}</v>
       </c>
-      <c r="G1" s="26"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="32" customHeight="1">
       <c r="A2" s="25" t="s">
@@ -3776,24 +3776,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="50" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="23" t="e" cm="1">
+      <c r="B1" s="23"/>
+      <c r="C1" s="24" t="e" cm="1">
         <f t="array" aca="1" ref="C1" ca="1">TBEG_IMAGE(ci)</f>
         <v>#NAME?</v>
       </c>
-      <c r="D1" s="23"/>
+      <c r="D1" s="24"/>
       <c r="E1" t="e" cm="1">
         <f t="array" aca="1" ref="E1" ca="1">TBEG_IMAGE(logo)</f>
         <v>#NAME?</v>
       </c>
-      <c r="F1" s="26" t="str">
+      <c r="F1" s="29" t="str">
         <f>HYPERLINK("${url}", "${linkText}")</f>
         <v>${linkText}</v>
       </c>
-      <c r="G1" s="26"/>
+      <c r="G1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="32" customHeight="1">
       <c r="A2" s="25" t="s">
